--- a/SubClase/ULA_SubClase.xlsx
+++ b/SubClase/ULA_SubClase.xlsx
@@ -680,13 +680,13 @@
         <v>1.542616477390242</v>
       </c>
       <c r="C2" s="2">
-        <v>108.2904632709742</v>
+        <v>107.8908157346848</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.670506529860277</v>
+        <v>1.664341501113992</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -779,7 +779,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>9.2149927963076</v>
+        <v>9.214992796307602</v>
       </c>
       <c r="C8" s="2">
         <v>111.359880556012</v>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="2">
-        <v>10.26180497121325</v>
+        <v>10.26180497121326</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1071,13 +1071,13 @@
         <v>2.911455503245201</v>
       </c>
       <c r="C25" s="2">
-        <v>106.8068182654629</v>
+        <v>106.806818265463</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="2">
-        <v>3.109632988230921</v>
+        <v>3.109632988230922</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1221,7 +1221,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>4.233805255668773</v>
+        <v>4.233805255668772</v>
       </c>
       <c r="C34" s="2">
         <v>128.6670324544963</v>
@@ -1230,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="2">
-        <v>5.447511582371509</v>
+        <v>5.447511582371508</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1408,7 +1408,7 @@
         <v>49</v>
       </c>
       <c r="B45" s="2">
-        <v>0.8759865797997735</v>
+        <v>0.8759865797997733</v>
       </c>
       <c r="C45" s="2">
         <v>115.2660548810867</v>
@@ -1527,7 +1527,7 @@
         <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6511549661138185</v>
+        <v>0.6511549661138186</v>
       </c>
       <c r="C52" s="2">
         <v>104.9713926386875</v>
@@ -1544,7 +1544,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="2">
-        <v>0.9708232464684994</v>
+        <v>0.9708232464684993</v>
       </c>
       <c r="C53" s="2">
         <v>104.1318720396006</v>
@@ -1680,7 +1680,7 @@
         <v>65</v>
       </c>
       <c r="B61" s="2">
-        <v>3.840631961716056</v>
+        <v>3.840631961716055</v>
       </c>
       <c r="C61" s="2">
         <v>110.3296953370247</v>
@@ -1876,7 +1876,7 @@
         <v>6</v>
       </c>
       <c r="E72" s="2">
-        <v>0.3036778664538096</v>
+        <v>0.3036778664538097</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1961,7 +1961,7 @@
         <v>6</v>
       </c>
       <c r="E77" s="2">
-        <v>3.142622910562886</v>
+        <v>3.142622910562887</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2108,7 +2108,7 @@
         <v>1.18674916526019</v>
       </c>
       <c r="C86" s="2">
-        <v>100.2918614187158</v>
+        <v>100.2918614187157</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>6</v>
@@ -2148,7 +2148,7 @@
         <v>6</v>
       </c>
       <c r="E88" s="2">
-        <v>1.729415562936943</v>
+        <v>1.729415562936944</v>
       </c>
     </row>
   </sheetData>
